--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861798</v>
       </c>
       <c r="B2" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126861856</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126861830</v>
       </c>
       <c r="B4" t="n">
-        <v>95218</v>
+        <v>95293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126861867</v>
       </c>
       <c r="B5" t="n">
-        <v>80018</v>
+        <v>80049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126861832</v>
       </c>
       <c r="B6" t="n">
-        <v>95218</v>
+        <v>95293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126861857</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126861851</v>
       </c>
       <c r="B8" t="n">
-        <v>98281</v>
+        <v>98356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126861802</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>126861828</v>
       </c>
       <c r="B10" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>126861850</v>
       </c>
       <c r="B11" t="n">
-        <v>98265</v>
+        <v>98340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861800</v>
+        <v>126861813</v>
       </c>
       <c r="B12" t="n">
-        <v>91210</v>
+        <v>98457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862727</v>
+        <v>862862</v>
       </c>
       <c r="R12" t="n">
-        <v>7322107</v>
+        <v>7322193</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861833</v>
+        <v>126861800</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>91284</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862829</v>
+        <v>862727</v>
       </c>
       <c r="R13" t="n">
-        <v>7322181</v>
+        <v>7322107</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861813</v>
+        <v>126861833</v>
       </c>
       <c r="B14" t="n">
-        <v>98382</v>
+        <v>80114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862862</v>
+        <v>862829</v>
       </c>
       <c r="R14" t="n">
-        <v>7322193</v>
+        <v>7322181</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126861829</v>
+        <v>126861811</v>
       </c>
       <c r="B15" t="n">
-        <v>98395</v>
+        <v>80143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862722</v>
+        <v>862829</v>
       </c>
       <c r="R15" t="n">
-        <v>7322141</v>
+        <v>7322181</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126861811</v>
+        <v>126861829</v>
       </c>
       <c r="B16" t="n">
-        <v>80112</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862829</v>
+        <v>862722</v>
       </c>
       <c r="R16" t="n">
-        <v>7322181</v>
+        <v>7322141</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2129,7 +2129,7 @@
         <v>126861854</v>
       </c>
       <c r="B17" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>126861858</v>
       </c>
       <c r="B18" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>126861831</v>
       </c>
       <c r="B19" t="n">
-        <v>95218</v>
+        <v>95293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>126861855</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861816</v>
+        <v>126861859</v>
       </c>
       <c r="B21" t="n">
-        <v>79987</v>
+        <v>82852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862903</v>
+        <v>862921</v>
       </c>
       <c r="R21" t="n">
-        <v>7322223</v>
+        <v>7322204</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861859</v>
+        <v>126861816</v>
       </c>
       <c r="B22" t="n">
-        <v>82792</v>
+        <v>80018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862921</v>
+        <v>862903</v>
       </c>
       <c r="R22" t="n">
-        <v>7322204</v>
+        <v>7322223</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861798</v>
       </c>
       <c r="B2" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126861856</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126861830</v>
+        <v>126861867</v>
       </c>
       <c r="B4" t="n">
-        <v>95293</v>
+        <v>80052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862724</v>
+        <v>862890</v>
       </c>
       <c r="R4" t="n">
-        <v>7322146</v>
+        <v>7322209</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126861867</v>
+        <v>126861830</v>
       </c>
       <c r="B5" t="n">
-        <v>80049</v>
+        <v>95299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>2387</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862890</v>
+        <v>862724</v>
       </c>
       <c r="R5" t="n">
-        <v>7322209</v>
+        <v>7322146</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126861832</v>
+        <v>126861857</v>
       </c>
       <c r="B6" t="n">
-        <v>95293</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862727</v>
+        <v>862847</v>
       </c>
       <c r="R6" t="n">
-        <v>7322104</v>
+        <v>7322167</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126861857</v>
+        <v>126861832</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>95299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862847</v>
+        <v>862727</v>
       </c>
       <c r="R7" t="n">
-        <v>7322167</v>
+        <v>7322104</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>126861851</v>
       </c>
       <c r="B8" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126861802</v>
       </c>
       <c r="B9" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>126861828</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861850</v>
+        <v>126861833</v>
       </c>
       <c r="B11" t="n">
-        <v>98340</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862717</v>
+        <v>862829</v>
       </c>
       <c r="R11" t="n">
-        <v>7322143</v>
+        <v>7322181</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861813</v>
+        <v>126861850</v>
       </c>
       <c r="B12" t="n">
-        <v>98457</v>
+        <v>98346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862862</v>
+        <v>862717</v>
       </c>
       <c r="R12" t="n">
-        <v>7322193</v>
+        <v>7322143</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861800</v>
+        <v>126861813</v>
       </c>
       <c r="B13" t="n">
-        <v>91284</v>
+        <v>98463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862727</v>
+        <v>862862</v>
       </c>
       <c r="R13" t="n">
-        <v>7322107</v>
+        <v>7322193</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861833</v>
+        <v>126861800</v>
       </c>
       <c r="B14" t="n">
-        <v>80114</v>
+        <v>91290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862829</v>
+        <v>862727</v>
       </c>
       <c r="R14" t="n">
-        <v>7322181</v>
+        <v>7322107</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1935,7 +1935,7 @@
         <v>126861811</v>
       </c>
       <c r="B15" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>126861829</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>126861854</v>
       </c>
       <c r="B17" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861858</v>
+        <v>126861855</v>
       </c>
       <c r="B18" t="n">
-        <v>82852</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862762</v>
+        <v>862777</v>
       </c>
       <c r="R18" t="n">
-        <v>7322183</v>
+        <v>7322177</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2323,7 +2323,7 @@
         <v>126861831</v>
       </c>
       <c r="B19" t="n">
-        <v>95293</v>
+        <v>95299</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126861855</v>
+        <v>126861858</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>82855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862777</v>
+        <v>862762</v>
       </c>
       <c r="R20" t="n">
-        <v>7322177</v>
+        <v>7322183</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861859</v>
+        <v>126861816</v>
       </c>
       <c r="B21" t="n">
-        <v>82852</v>
+        <v>80021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862921</v>
+        <v>862903</v>
       </c>
       <c r="R21" t="n">
-        <v>7322204</v>
+        <v>7322223</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861816</v>
+        <v>126861859</v>
       </c>
       <c r="B22" t="n">
-        <v>80018</v>
+        <v>82855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862903</v>
+        <v>862921</v>
       </c>
       <c r="R22" t="n">
-        <v>7322223</v>
+        <v>7322204</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126861867</v>
+        <v>126861830</v>
       </c>
       <c r="B4" t="n">
-        <v>80052</v>
+        <v>95299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>2387</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862890</v>
+        <v>862724</v>
       </c>
       <c r="R4" t="n">
-        <v>7322209</v>
+        <v>7322146</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126861830</v>
+        <v>126861867</v>
       </c>
       <c r="B5" t="n">
-        <v>95299</v>
+        <v>80052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2387</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862724</v>
+        <v>862890</v>
       </c>
       <c r="R5" t="n">
-        <v>7322146</v>
+        <v>7322209</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126861832</v>
+        <v>126861851</v>
       </c>
       <c r="B7" t="n">
-        <v>95299</v>
+        <v>98362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,23 +1171,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2387</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1195,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862727</v>
+        <v>862821</v>
       </c>
       <c r="R7" t="n">
-        <v>7322104</v>
+        <v>7322190</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1257,10 +1253,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126861851</v>
+        <v>126861832</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>95299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,19 +1264,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>2387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862821</v>
+        <v>862727</v>
       </c>
       <c r="R8" t="n">
-        <v>7322190</v>
+        <v>7322104</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861833</v>
+        <v>126861850</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>98346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862829</v>
+        <v>862717</v>
       </c>
       <c r="R11" t="n">
-        <v>7322181</v>
+        <v>7322143</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861850</v>
+        <v>126861813</v>
       </c>
       <c r="B12" t="n">
-        <v>98346</v>
+        <v>98463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862717</v>
+        <v>862862</v>
       </c>
       <c r="R12" t="n">
-        <v>7322143</v>
+        <v>7322193</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861813</v>
+        <v>126861800</v>
       </c>
       <c r="B13" t="n">
-        <v>98463</v>
+        <v>91290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862862</v>
+        <v>862727</v>
       </c>
       <c r="R13" t="n">
-        <v>7322193</v>
+        <v>7322107</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861800</v>
+        <v>126861833</v>
       </c>
       <c r="B14" t="n">
-        <v>91290</v>
+        <v>80117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862727</v>
+        <v>862829</v>
       </c>
       <c r="R14" t="n">
-        <v>7322107</v>
+        <v>7322181</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2223,32 +2223,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861855</v>
+        <v>126861831</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>95299</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862777</v>
+        <v>862814</v>
       </c>
       <c r="R18" t="n">
-        <v>7322177</v>
+        <v>7322193</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,32 +2320,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861831</v>
+        <v>126861858</v>
       </c>
       <c r="B19" t="n">
-        <v>95299</v>
+        <v>82855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862814</v>
+        <v>862762</v>
       </c>
       <c r="R19" t="n">
-        <v>7322193</v>
+        <v>7322183</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126861858</v>
+        <v>126861855</v>
       </c>
       <c r="B20" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862762</v>
+        <v>862777</v>
       </c>
       <c r="R20" t="n">
-        <v>7322183</v>
+        <v>7322177</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861816</v>
+        <v>126861859</v>
       </c>
       <c r="B21" t="n">
-        <v>80021</v>
+        <v>82855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862903</v>
+        <v>862921</v>
       </c>
       <c r="R21" t="n">
-        <v>7322223</v>
+        <v>7322204</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861859</v>
+        <v>126861816</v>
       </c>
       <c r="B22" t="n">
-        <v>82855</v>
+        <v>80021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862921</v>
+        <v>862903</v>
       </c>
       <c r="R22" t="n">
-        <v>7322204</v>
+        <v>7322223</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861798</v>
       </c>
       <c r="B2" t="n">
-        <v>105462</v>
+        <v>105463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126861830</v>
       </c>
       <c r="B4" t="n">
-        <v>95299</v>
+        <v>95300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126861857</v>
+        <v>126861832</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>95300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862847</v>
+        <v>862727</v>
       </c>
       <c r="R6" t="n">
-        <v>7322167</v>
+        <v>7322104</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,30 +1160,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126861851</v>
+        <v>126861857</v>
       </c>
       <c r="B7" t="n">
-        <v>98362</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1191,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862821</v>
+        <v>862847</v>
       </c>
       <c r="R7" t="n">
-        <v>7322190</v>
+        <v>7322167</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1253,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126861832</v>
+        <v>126861851</v>
       </c>
       <c r="B8" t="n">
-        <v>95299</v>
+        <v>98363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,23 +1268,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862727</v>
+        <v>862821</v>
       </c>
       <c r="R8" t="n">
-        <v>7322104</v>
+        <v>7322190</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1353,7 +1353,7 @@
         <v>126861802</v>
       </c>
       <c r="B9" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>126861828</v>
       </c>
       <c r="B10" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861850</v>
+        <v>126861833</v>
       </c>
       <c r="B11" t="n">
-        <v>98346</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862717</v>
+        <v>862829</v>
       </c>
       <c r="R11" t="n">
-        <v>7322143</v>
+        <v>7322181</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1644,7 +1644,7 @@
         <v>126861813</v>
       </c>
       <c r="B12" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>126861800</v>
       </c>
       <c r="B13" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861833</v>
+        <v>126861850</v>
       </c>
       <c r="B14" t="n">
-        <v>80117</v>
+        <v>98347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862829</v>
+        <v>862717</v>
       </c>
       <c r="R14" t="n">
-        <v>7322181</v>
+        <v>7322143</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2032,7 +2032,7 @@
         <v>126861829</v>
       </c>
       <c r="B16" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>126861854</v>
       </c>
       <c r="B17" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2223,32 +2223,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861831</v>
+        <v>126861858</v>
       </c>
       <c r="B18" t="n">
-        <v>95299</v>
+        <v>82855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862814</v>
+        <v>862762</v>
       </c>
       <c r="R18" t="n">
-        <v>7322193</v>
+        <v>7322183</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,32 +2320,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861858</v>
+        <v>126861831</v>
       </c>
       <c r="B19" t="n">
-        <v>82855</v>
+        <v>95300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862762</v>
+        <v>862814</v>
       </c>
       <c r="R19" t="n">
-        <v>7322183</v>
+        <v>7322193</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861859</v>
+        <v>126861816</v>
       </c>
       <c r="B21" t="n">
-        <v>82855</v>
+        <v>80021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862921</v>
+        <v>862903</v>
       </c>
       <c r="R21" t="n">
-        <v>7322204</v>
+        <v>7322223</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861816</v>
+        <v>126861859</v>
       </c>
       <c r="B22" t="n">
-        <v>80021</v>
+        <v>82855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862903</v>
+        <v>862921</v>
       </c>
       <c r="R22" t="n">
-        <v>7322223</v>
+        <v>7322204</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -2223,32 +2223,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861858</v>
+        <v>126861831</v>
       </c>
       <c r="B18" t="n">
-        <v>82855</v>
+        <v>95300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862762</v>
+        <v>862814</v>
       </c>
       <c r="R18" t="n">
-        <v>7322183</v>
+        <v>7322193</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,32 +2320,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861831</v>
+        <v>126861855</v>
       </c>
       <c r="B19" t="n">
-        <v>95300</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862814</v>
+        <v>862777</v>
       </c>
       <c r="R19" t="n">
-        <v>7322193</v>
+        <v>7322177</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126861855</v>
+        <v>126861858</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862777</v>
+        <v>862762</v>
       </c>
       <c r="R20" t="n">
-        <v>7322177</v>
+        <v>7322183</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126861830</v>
+        <v>126861867</v>
       </c>
       <c r="B4" t="n">
-        <v>95300</v>
+        <v>80052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862724</v>
+        <v>862890</v>
       </c>
       <c r="R4" t="n">
-        <v>7322146</v>
+        <v>7322209</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126861867</v>
+        <v>126861830</v>
       </c>
       <c r="B5" t="n">
-        <v>80052</v>
+        <v>95300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>2387</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862890</v>
+        <v>862724</v>
       </c>
       <c r="R5" t="n">
-        <v>7322209</v>
+        <v>7322146</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861833</v>
+        <v>126861800</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>91291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862829</v>
+        <v>862727</v>
       </c>
       <c r="R11" t="n">
-        <v>7322181</v>
+        <v>7322107</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861813</v>
+        <v>126861833</v>
       </c>
       <c r="B12" t="n">
-        <v>98464</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862862</v>
+        <v>862829</v>
       </c>
       <c r="R12" t="n">
-        <v>7322193</v>
+        <v>7322181</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861800</v>
+        <v>126861813</v>
       </c>
       <c r="B13" t="n">
-        <v>91291</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862727</v>
+        <v>862862</v>
       </c>
       <c r="R13" t="n">
-        <v>7322107</v>
+        <v>7322193</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126861811</v>
+        <v>126861829</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>98477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862829</v>
+        <v>862722</v>
       </c>
       <c r="R15" t="n">
-        <v>7322181</v>
+        <v>7322141</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126861829</v>
+        <v>126861811</v>
       </c>
       <c r="B16" t="n">
-        <v>98477</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862722</v>
+        <v>862829</v>
       </c>
       <c r="R16" t="n">
-        <v>7322141</v>
+        <v>7322181</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861855</v>
+        <v>126861858</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2331,21 +2331,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862777</v>
+        <v>862762</v>
       </c>
       <c r="R19" t="n">
-        <v>7322177</v>
+        <v>7322183</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126861858</v>
+        <v>126861855</v>
       </c>
       <c r="B20" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862762</v>
+        <v>862777</v>
       </c>
       <c r="R20" t="n">
-        <v>7322183</v>
+        <v>7322177</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861816</v>
+        <v>126861859</v>
       </c>
       <c r="B21" t="n">
-        <v>80021</v>
+        <v>82855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862903</v>
+        <v>862921</v>
       </c>
       <c r="R21" t="n">
-        <v>7322223</v>
+        <v>7322204</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861859</v>
+        <v>126861816</v>
       </c>
       <c r="B22" t="n">
-        <v>82855</v>
+        <v>80021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862921</v>
+        <v>862903</v>
       </c>
       <c r="R22" t="n">
-        <v>7322204</v>
+        <v>7322223</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126861867</v>
+        <v>126861830</v>
       </c>
       <c r="B4" t="n">
-        <v>80052</v>
+        <v>95300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>2387</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862890</v>
+        <v>862724</v>
       </c>
       <c r="R4" t="n">
-        <v>7322209</v>
+        <v>7322146</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126861830</v>
+        <v>126861867</v>
       </c>
       <c r="B5" t="n">
-        <v>95300</v>
+        <v>80052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2387</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862724</v>
+        <v>862890</v>
       </c>
       <c r="R5" t="n">
-        <v>7322146</v>
+        <v>7322209</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126861832</v>
+        <v>126861851</v>
       </c>
       <c r="B6" t="n">
-        <v>95300</v>
+        <v>98363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,23 +1074,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2387</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1098,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862727</v>
+        <v>862821</v>
       </c>
       <c r="R6" t="n">
-        <v>7322104</v>
+        <v>7322190</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1156,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126861857</v>
+        <v>126861832</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>95300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862847</v>
+        <v>862727</v>
       </c>
       <c r="R7" t="n">
-        <v>7322167</v>
+        <v>7322104</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1257,30 +1253,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126861851</v>
+        <v>126861857</v>
       </c>
       <c r="B8" t="n">
-        <v>98363</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862821</v>
+        <v>862847</v>
       </c>
       <c r="R8" t="n">
-        <v>7322190</v>
+        <v>7322167</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861813</v>
+        <v>126861850</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>98347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862862</v>
+        <v>862717</v>
       </c>
       <c r="R13" t="n">
-        <v>7322193</v>
+        <v>7322143</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861850</v>
+        <v>126861813</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98464</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,21 +1846,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862717</v>
+        <v>862862</v>
       </c>
       <c r="R14" t="n">
-        <v>7322143</v>
+        <v>7322193</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126861829</v>
+        <v>126861811</v>
       </c>
       <c r="B15" t="n">
-        <v>98477</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862722</v>
+        <v>862829</v>
       </c>
       <c r="R15" t="n">
-        <v>7322141</v>
+        <v>7322181</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126861811</v>
+        <v>126861829</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>98477</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862829</v>
+        <v>862722</v>
       </c>
       <c r="R16" t="n">
-        <v>7322181</v>
+        <v>7322141</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2223,32 +2223,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861831</v>
+        <v>126861858</v>
       </c>
       <c r="B18" t="n">
-        <v>95300</v>
+        <v>82855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862814</v>
+        <v>862762</v>
       </c>
       <c r="R18" t="n">
-        <v>7322193</v>
+        <v>7322183</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,32 +2320,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861858</v>
+        <v>126861831</v>
       </c>
       <c r="B19" t="n">
-        <v>82855</v>
+        <v>95300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862762</v>
+        <v>862814</v>
       </c>
       <c r="R19" t="n">
-        <v>7322183</v>
+        <v>7322193</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861850</v>
+        <v>126861813</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862717</v>
+        <v>862862</v>
       </c>
       <c r="R13" t="n">
-        <v>7322143</v>
+        <v>7322193</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861813</v>
+        <v>126861850</v>
       </c>
       <c r="B14" t="n">
-        <v>98464</v>
+        <v>98347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,21 +1846,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862862</v>
+        <v>862717</v>
       </c>
       <c r="R14" t="n">
-        <v>7322193</v>
+        <v>7322143</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126861811</v>
+        <v>126861829</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>98477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862829</v>
+        <v>862722</v>
       </c>
       <c r="R15" t="n">
-        <v>7322181</v>
+        <v>7322141</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126861829</v>
+        <v>126861811</v>
       </c>
       <c r="B16" t="n">
-        <v>98477</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862722</v>
+        <v>862829</v>
       </c>
       <c r="R16" t="n">
-        <v>7322141</v>
+        <v>7322181</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861798</v>
       </c>
       <c r="B2" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126861856</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126861830</v>
       </c>
       <c r="B4" t="n">
-        <v>95300</v>
+        <v>95304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126861867</v>
       </c>
       <c r="B5" t="n">
-        <v>80052</v>
+        <v>80056</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126861851</v>
       </c>
       <c r="B6" t="n">
-        <v>98363</v>
+        <v>98367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,32 +1156,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126861832</v>
+        <v>126861857</v>
       </c>
       <c r="B7" t="n">
-        <v>95300</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862727</v>
+        <v>862847</v>
       </c>
       <c r="R7" t="n">
-        <v>7322104</v>
+        <v>7322167</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1253,32 +1253,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126861857</v>
+        <v>126861832</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>95304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862847</v>
+        <v>862727</v>
       </c>
       <c r="R8" t="n">
-        <v>7322167</v>
+        <v>7322104</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1353,7 +1353,7 @@
         <v>126861802</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>126861828</v>
       </c>
       <c r="B10" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861800</v>
+        <v>126861850</v>
       </c>
       <c r="B11" t="n">
-        <v>91291</v>
+        <v>98351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862727</v>
+        <v>862717</v>
       </c>
       <c r="R11" t="n">
-        <v>7322107</v>
+        <v>7322143</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861833</v>
+        <v>126861800</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>91295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862829</v>
+        <v>862727</v>
       </c>
       <c r="R12" t="n">
-        <v>7322181</v>
+        <v>7322107</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861813</v>
+        <v>126861833</v>
       </c>
       <c r="B13" t="n">
-        <v>98464</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862862</v>
+        <v>862829</v>
       </c>
       <c r="R13" t="n">
-        <v>7322193</v>
+        <v>7322181</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861850</v>
+        <v>126861813</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,21 +1846,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862717</v>
+        <v>862862</v>
       </c>
       <c r="R14" t="n">
-        <v>7322143</v>
+        <v>7322193</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126861829</v>
+        <v>126861811</v>
       </c>
       <c r="B15" t="n">
-        <v>98477</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862722</v>
+        <v>862829</v>
       </c>
       <c r="R15" t="n">
-        <v>7322141</v>
+        <v>7322181</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126861811</v>
+        <v>126861829</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>98481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862829</v>
+        <v>862722</v>
       </c>
       <c r="R16" t="n">
-        <v>7322181</v>
+        <v>7322141</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2129,7 +2129,7 @@
         <v>126861854</v>
       </c>
       <c r="B17" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861858</v>
+        <v>126861855</v>
       </c>
       <c r="B18" t="n">
-        <v>82855</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2234,21 +2234,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862762</v>
+        <v>862777</v>
       </c>
       <c r="R18" t="n">
-        <v>7322183</v>
+        <v>7322177</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,32 +2320,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861831</v>
+        <v>126861858</v>
       </c>
       <c r="B19" t="n">
-        <v>95300</v>
+        <v>82859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862814</v>
+        <v>862762</v>
       </c>
       <c r="R19" t="n">
-        <v>7322193</v>
+        <v>7322183</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2417,32 +2417,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126861855</v>
+        <v>126861831</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>95304</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862777</v>
+        <v>862814</v>
       </c>
       <c r="R20" t="n">
-        <v>7322177</v>
+        <v>7322193</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861859</v>
+        <v>126861816</v>
       </c>
       <c r="B21" t="n">
-        <v>82855</v>
+        <v>80025</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862921</v>
+        <v>862903</v>
       </c>
       <c r="R21" t="n">
-        <v>7322204</v>
+        <v>7322223</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861816</v>
+        <v>126861859</v>
       </c>
       <c r="B22" t="n">
-        <v>80021</v>
+        <v>82859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862903</v>
+        <v>862921</v>
       </c>
       <c r="R22" t="n">
-        <v>7322223</v>
+        <v>7322204</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -1063,30 +1063,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126861851</v>
+        <v>126861857</v>
       </c>
       <c r="B6" t="n">
-        <v>98367</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1094,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862821</v>
+        <v>862847</v>
       </c>
       <c r="R6" t="n">
-        <v>7322190</v>
+        <v>7322167</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1156,34 +1160,30 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126861857</v>
+        <v>126861851</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>98367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862847</v>
+        <v>862821</v>
       </c>
       <c r="R7" t="n">
-        <v>7322167</v>
+        <v>7322190</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861850</v>
+        <v>126861800</v>
       </c>
       <c r="B11" t="n">
-        <v>98351</v>
+        <v>91295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862717</v>
+        <v>862727</v>
       </c>
       <c r="R11" t="n">
-        <v>7322143</v>
+        <v>7322107</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861800</v>
+        <v>126861833</v>
       </c>
       <c r="B12" t="n">
-        <v>91295</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862727</v>
+        <v>862829</v>
       </c>
       <c r="R12" t="n">
-        <v>7322107</v>
+        <v>7322181</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861833</v>
+        <v>126861850</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>98351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862829</v>
+        <v>862717</v>
       </c>
       <c r="R13" t="n">
-        <v>7322181</v>
+        <v>7322143</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2223,32 +2223,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861855</v>
+        <v>126861831</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>95304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862777</v>
+        <v>862814</v>
       </c>
       <c r="R18" t="n">
-        <v>7322177</v>
+        <v>7322193</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2417,32 +2417,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126861831</v>
+        <v>126861855</v>
       </c>
       <c r="B20" t="n">
-        <v>95304</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>862814</v>
+        <v>862777</v>
       </c>
       <c r="R20" t="n">
-        <v>7322193</v>
+        <v>7322177</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126861816</v>
+        <v>126861859</v>
       </c>
       <c r="B21" t="n">
-        <v>80025</v>
+        <v>82859</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>862903</v>
+        <v>862921</v>
       </c>
       <c r="R21" t="n">
-        <v>7322223</v>
+        <v>7322204</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2611,32 +2611,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126861859</v>
+        <v>126861816</v>
       </c>
       <c r="B22" t="n">
-        <v>82859</v>
+        <v>80025</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>862921</v>
+        <v>862903</v>
       </c>
       <c r="R22" t="n">
-        <v>7322204</v>
+        <v>7322223</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126861857</v>
+        <v>126861832</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>95304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862847</v>
+        <v>862727</v>
       </c>
       <c r="R6" t="n">
-        <v>7322167</v>
+        <v>7322104</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,30 +1160,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126861851</v>
+        <v>126861857</v>
       </c>
       <c r="B7" t="n">
-        <v>98367</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1191,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862821</v>
+        <v>862847</v>
       </c>
       <c r="R7" t="n">
-        <v>7322190</v>
+        <v>7322167</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1253,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126861832</v>
+        <v>126861851</v>
       </c>
       <c r="B8" t="n">
-        <v>95304</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,23 +1268,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Huebener) T.J.Kop.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862727</v>
+        <v>862821</v>
       </c>
       <c r="R8" t="n">
-        <v>7322104</v>
+        <v>7322190</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861800</v>
+        <v>126861813</v>
       </c>
       <c r="B11" t="n">
-        <v>91295</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862727</v>
+        <v>862862</v>
       </c>
       <c r="R11" t="n">
-        <v>7322107</v>
+        <v>7322193</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,32 +1641,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861833</v>
+        <v>126861850</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>98351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862829</v>
+        <v>862717</v>
       </c>
       <c r="R12" t="n">
-        <v>7322181</v>
+        <v>7322143</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861850</v>
+        <v>126861800</v>
       </c>
       <c r="B13" t="n">
-        <v>98351</v>
+        <v>91295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862717</v>
+        <v>862727</v>
       </c>
       <c r="R13" t="n">
-        <v>7322143</v>
+        <v>7322107</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861813</v>
+        <v>126861833</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>80121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862862</v>
+        <v>862829</v>
       </c>
       <c r="R14" t="n">
-        <v>7322193</v>
+        <v>7322181</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2223,32 +2223,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861831</v>
+        <v>126861858</v>
       </c>
       <c r="B18" t="n">
-        <v>95304</v>
+        <v>82859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862814</v>
+        <v>862762</v>
       </c>
       <c r="R18" t="n">
-        <v>7322193</v>
+        <v>7322183</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,32 +2320,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861858</v>
+        <v>126861831</v>
       </c>
       <c r="B19" t="n">
-        <v>82859</v>
+        <v>95304</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862762</v>
+        <v>862814</v>
       </c>
       <c r="R19" t="n">
-        <v>7322183</v>
+        <v>7322193</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126861811</v>
+        <v>126861829</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>98481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862829</v>
+        <v>862722</v>
       </c>
       <c r="R15" t="n">
-        <v>7322181</v>
+        <v>7322141</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126861829</v>
+        <v>126861811</v>
       </c>
       <c r="B16" t="n">
-        <v>98481</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862722</v>
+        <v>862829</v>
       </c>
       <c r="R16" t="n">
-        <v>7322141</v>
+        <v>7322181</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861798</v>
       </c>
       <c r="B2" t="n">
-        <v>105469</v>
+        <v>105471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126861851</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>98368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>126861828</v>
       </c>
       <c r="B10" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861813</v>
+        <v>126861850</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1555,21 +1555,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862862</v>
+        <v>862717</v>
       </c>
       <c r="R11" t="n">
-        <v>7322193</v>
+        <v>7322143</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126861850</v>
+        <v>126861813</v>
       </c>
       <c r="B12" t="n">
-        <v>98351</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862717</v>
+        <v>862862</v>
       </c>
       <c r="R12" t="n">
-        <v>7322143</v>
+        <v>7322193</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861800</v>
+        <v>126861833</v>
       </c>
       <c r="B13" t="n">
-        <v>91295</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862727</v>
+        <v>862829</v>
       </c>
       <c r="R13" t="n">
-        <v>7322107</v>
+        <v>7322181</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,32 +1835,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861833</v>
+        <v>126861800</v>
       </c>
       <c r="B14" t="n">
-        <v>80121</v>
+        <v>91295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862829</v>
+        <v>862727</v>
       </c>
       <c r="R14" t="n">
-        <v>7322181</v>
+        <v>7322107</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1935,7 +1935,7 @@
         <v>126861829</v>
       </c>
       <c r="B15" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2223,32 +2223,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126861858</v>
+        <v>126861831</v>
       </c>
       <c r="B18" t="n">
-        <v>82859</v>
+        <v>95304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>862762</v>
+        <v>862814</v>
       </c>
       <c r="R18" t="n">
-        <v>7322183</v>
+        <v>7322193</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,32 +2320,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126861831</v>
+        <v>126861858</v>
       </c>
       <c r="B19" t="n">
-        <v>95304</v>
+        <v>82859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>862814</v>
+        <v>862762</v>
       </c>
       <c r="R19" t="n">
-        <v>7322193</v>
+        <v>7322183</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -1544,32 +1544,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126861850</v>
+        <v>126861833</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862717</v>
+        <v>862829</v>
       </c>
       <c r="R11" t="n">
-        <v>7322143</v>
+        <v>7322181</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1738,32 +1738,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861833</v>
+        <v>126861800</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>91295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862829</v>
+        <v>862727</v>
       </c>
       <c r="R13" t="n">
-        <v>7322181</v>
+        <v>7322107</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126861800</v>
+        <v>126861850</v>
       </c>
       <c r="B14" t="n">
-        <v>91295</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,21 +1846,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862727</v>
+        <v>862717</v>
       </c>
       <c r="R14" t="n">
-        <v>7322107</v>
+        <v>7322143</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126861829</v>
+        <v>126861811</v>
       </c>
       <c r="B15" t="n">
-        <v>98482</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862722</v>
+        <v>862829</v>
       </c>
       <c r="R15" t="n">
-        <v>7322141</v>
+        <v>7322181</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126861811</v>
+        <v>126861829</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>98482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>862829</v>
+        <v>862722</v>
       </c>
       <c r="R16" t="n">
-        <v>7322181</v>
+        <v>7322141</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98482</v>
+        <v>98484</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98490</v>
+        <v>98493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27927-2025 artfynd.xlsx
+++ b/artfynd/A 27927-2025 artfynd.xlsx
@@ -2711,7 +2711,7 @@
         <v>126861827</v>
       </c>
       <c r="B23" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
